--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488239_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488239_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.937900000000001</v>
+        <v>9.5753</v>
       </c>
       <c r="E2" t="n">
-        <v>5.0953</v>
+        <v>5.3141</v>
       </c>
       <c r="F2" t="n">
-        <v>3.8427</v>
+        <v>4.2612</v>
       </c>
       <c r="G2" t="n">
         <v>5.3276</v>
@@ -610,13 +610,13 @@
         <v>2.7793</v>
       </c>
       <c r="S2" t="n">
-        <v>0.667</v>
+        <v>1.3045</v>
       </c>
       <c r="T2" t="n">
-        <v>0.8431</v>
+        <v>1.062</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1761</v>
+        <v>0.2425</v>
       </c>
       <c r="V2" t="n">
         <v>2.2022</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.9766</v>
+        <v>6.9443</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7028</v>
+        <v>3.769</v>
       </c>
       <c r="F3" t="n">
-        <v>3.2738</v>
+        <v>3.1753</v>
       </c>
       <c r="G3" t="n">
         <v>4.9598</v>
@@ -688,13 +688,13 @@
         <v>1.6676</v>
       </c>
       <c r="S3" t="n">
-        <v>0.8309</v>
+        <v>0.7987</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2574</v>
+        <v>0.3236</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5735</v>
+        <v>0.475</v>
       </c>
       <c r="V3" t="n">
         <v>0.63</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>5.7361</v>
+        <v>6.7838</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8069</v>
+        <v>2.4607</v>
       </c>
       <c r="F4" t="n">
-        <v>3.9292</v>
+        <v>4.3232</v>
       </c>
       <c r="G4" t="n">
         <v>5.5918</v>
@@ -766,13 +766,13 @@
         <v>2.9646</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1875</v>
+        <v>0.8602</v>
       </c>
       <c r="T4" t="n">
-        <v>0.4091</v>
+        <v>1.0629</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5967</v>
+        <v>-0.2027</v>
       </c>
       <c r="V4" t="n">
         <v>1.2583</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.1308</v>
+        <v>3.2927</v>
       </c>
       <c r="E5" t="n">
-        <v>0.998</v>
+        <v>1.5539</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1328</v>
+        <v>1.7389</v>
       </c>
       <c r="G5" t="n">
         <v>3.994</v>
@@ -844,13 +844,13 @@
         <v>1.4823</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6377</v>
+        <v>0.7996</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.286</v>
+        <v>0.2699</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9237</v>
+        <v>0.5296999999999999</v>
       </c>
       <c r="V5" t="n">
         <v>-0.945</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.0296</v>
+        <v>1.5885</v>
       </c>
       <c r="E6" t="n">
-        <v>4.9417</v>
+        <v>3.9192</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.9121</v>
+        <v>-2.3307</v>
       </c>
       <c r="G6" t="n">
         <v>-0.7175</v>
@@ -922,13 +922,13 @@
         <v>2.4087</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5973</v>
+        <v>1.1562</v>
       </c>
       <c r="T6" t="n">
-        <v>2.3677</v>
+        <v>1.3452</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2295</v>
+        <v>-0.189</v>
       </c>
       <c r="V6" t="n">
         <v>-1.2589</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3554</v>
+        <v>-0.7612</v>
       </c>
       <c r="E7" t="n">
-        <v>1.0182</v>
+        <v>1.4647</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.3736</v>
+        <v>-2.2259</v>
       </c>
       <c r="G7" t="n">
         <v>-1.6116</v>
@@ -1000,13 +1000,13 @@
         <v>2.0382</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2087</v>
+        <v>0.3855</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4974</v>
+        <v>0.9439</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.7060999999999999</v>
+        <v>-0.5584</v>
       </c>
       <c r="V7" t="n">
         <v>-1.5733</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3641</v>
+        <v>-1.3581</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0567</v>
+        <v>-1.0999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3074</v>
+        <v>-0.2582</v>
       </c>
       <c r="G8" t="n">
         <v>-1.8538</v>
@@ -1078,13 +1078,13 @@
         <v>2.4087</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5638</v>
+        <v>0.5699</v>
       </c>
       <c r="T8" t="n">
-        <v>1.1167</v>
+        <v>1.0735</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5528999999999999</v>
+        <v>-0.5036</v>
       </c>
       <c r="V8" t="n">
         <v>-0.63</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.5553</v>
+        <v>-1.6915</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.5383</v>
+        <v>-3.5268</v>
       </c>
       <c r="F9" t="n">
-        <v>1.9831</v>
+        <v>1.8354</v>
       </c>
       <c r="G9" t="n">
         <v>-2.4492</v>
@@ -1156,13 +1156,13 @@
         <v>1.6676</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6339</v>
+        <v>0.4977</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5521</v>
+        <v>0.5636</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0818</v>
+        <v>-0.0659</v>
       </c>
       <c r="V9" t="n">
         <v>0.6304999999999999</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. TORRES VELEZ</t>
+          <t>T. LUCERO BARBEITO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,31 +1189,31 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7273</v>
+        <v>-2.8042</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.7506</v>
+        <v>-0.038</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9767</v>
+        <v>-2.7662</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.1878</v>
+        <v>-3.3382</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2756</v>
+        <v>-0.6192</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.9122</v>
+        <v>-2.719</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7354000000000001</v>
+        <v>-0.4149</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5281</v>
+        <v>0.1845</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2074</v>
+        <v>-0.5995</v>
       </c>
       <c r="M10" t="n">
         <v>-2.9233</v>
@@ -1225,37 +1225,37 @@
         <v>-2.1196</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.7411</v>
+        <v>0.9264</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1117</v>
+        <v>0.9264</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2017</v>
+        <v>-0.078</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3669</v>
+        <v>0.0625</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1652</v>
+        <v>-0.1405</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-0.6289</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. LUCERO BARBEITO</t>
+          <t>J. TORRES VELEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,31 +1267,31 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1774</v>
+        <v>-2.8438</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3865</v>
+        <v>-0.8917</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.7909</v>
+        <v>-1.9521</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.3382</v>
+        <v>-2.1878</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6192</v>
+        <v>-0.2756</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.719</v>
+        <v>-1.9122</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.4149</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1845</v>
+        <v>0.5281</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5995</v>
+        <v>0.2074</v>
       </c>
       <c r="M11" t="n">
         <v>-2.9233</v>
@@ -1303,31 +1303,31 @@
         <v>-2.1196</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9264</v>
+        <v>-0.7411</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9264</v>
+        <v>1.1117</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.4512</v>
+        <v>0.0852</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.286</v>
+        <v>0.2257</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1652</v>
+        <v>-0.1405</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.6289</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>17.6315</v>
+        <v>18.7258</v>
       </c>
       <c r="E12" t="n">
-        <v>11.8308</v>
+        <v>12.9252</v>
       </c>
       <c r="F12" t="n">
         <v>5.8009</v>
       </c>
       <c r="G12" t="n">
-        <v>7.715100000000003</v>
+        <v>7.715100000000004</v>
       </c>
       <c r="H12" t="n">
         <v>2.1471</v>
@@ -1390,13 +1390,13 @@
         <v>19.4551</v>
       </c>
       <c r="S12" t="n">
-        <v>5.2849</v>
+        <v>6.379499999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>5.838400000000001</v>
+        <v>6.932799999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5537</v>
+        <v>-0.5534</v>
       </c>
       <c r="V12" t="n">
         <v>-0.0005999999999999339</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.346</v>
+        <v>3.1283</v>
       </c>
       <c r="E13" t="n">
-        <v>2.7697</v>
+        <v>2.9655</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.4237</v>
+        <v>0.1628</v>
       </c>
       <c r="G13" t="n">
         <v>2.8797</v>
@@ -1468,13 +1468,13 @@
         <v>2.7793</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6623</v>
+        <v>0.12</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1567</v>
+        <v>0.3526</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.819</v>
+        <v>-0.2326</v>
       </c>
       <c r="V13" t="n">
         <v>0.3139</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.6049</v>
+        <v>0.6904</v>
       </c>
       <c r="E14" t="n">
-        <v>2.6144</v>
+        <v>1.1455</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0095</v>
+        <v>-0.4551</v>
       </c>
       <c r="G14" t="n">
         <v>0.128</v>
@@ -1546,13 +1546,13 @@
         <v>2.0382</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4589</v>
+        <v>0.5444</v>
       </c>
       <c r="T14" t="n">
-        <v>2.4983</v>
+        <v>1.0294</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0394</v>
+        <v>-0.485</v>
       </c>
       <c r="V14" t="n">
         <v>0.9444</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. CARRETERO GONZALEZ</t>
+          <t>J. RIBEIROS CARREIRAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.8096</v>
+        <v>-0.3193</v>
       </c>
       <c r="E16" t="n">
-        <v>0.0589</v>
+        <v>1.2243</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.8685</v>
+        <v>-1.5435</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.4127</v>
+        <v>2.7617</v>
       </c>
       <c r="H16" t="n">
-        <v>0.73</v>
+        <v>0.5026</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.1427</v>
+        <v>2.2592</v>
       </c>
       <c r="J16" t="n">
-        <v>0.837</v>
+        <v>4.7765</v>
       </c>
       <c r="K16" t="n">
-        <v>1.3654</v>
+        <v>1.55</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.5284</v>
+        <v>3.2266</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.2497</v>
+        <v>-2.0148</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.6354</v>
+        <v>-1.0474</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6143</v>
+        <v>-0.9674</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1853</v>
+        <v>-1.8529</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1117</v>
+        <v>-3.891</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9264</v>
+        <v>2.0382</v>
       </c>
       <c r="S16" t="n">
-        <v>0.4183</v>
+        <v>-0.9137</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6491</v>
+        <v>-0.2906</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2308</v>
+        <v>-0.623</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.63</v>
+        <v>-0.3144</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3155</v>
+        <v>0.6294</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.3144</v>
+        <v>-0.9439</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. GALLEGO CONTRERAS</t>
+          <t>D. LEMOINE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.0203</v>
+        <v>-0.5452</v>
       </c>
       <c r="E17" t="n">
-        <v>0.387</v>
+        <v>-2.4712</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.4073</v>
+        <v>1.9261</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.3941</v>
+        <v>-1.1922</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9088000000000001</v>
+        <v>0.2716</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4853</v>
+        <v>-1.4638</v>
       </c>
       <c r="J17" t="n">
-        <v>0.1172</v>
+        <v>-1.8312</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0342</v>
+        <v>0.0859</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0829</v>
+        <v>-1.9171</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5113</v>
+        <v>0.639</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.9429999999999999</v>
+        <v>0.1857</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.5683</v>
+        <v>0.4533</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>-0.1853</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-1.8529</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.6676</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3738</v>
+        <v>-0.4265</v>
       </c>
       <c r="T17" t="n">
-        <v>0.2699</v>
+        <v>-0.046</v>
       </c>
       <c r="U17" t="n">
-        <v>0.104</v>
+        <v>-0.3805</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. LEMOINE</t>
+          <t>R. CARRETERO GONZALEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5823</v>
+        <v>-1.112</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.863</v>
+        <v>-0.4308</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2807</v>
+        <v>-0.6812</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.1922</v>
+        <v>-0.4127</v>
       </c>
       <c r="H18" t="n">
-        <v>0.2716</v>
+        <v>0.73</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.4638</v>
+        <v>-1.1427</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.8312</v>
+        <v>0.837</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0859</v>
+        <v>1.3654</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.9171</v>
+        <v>-0.5284</v>
       </c>
       <c r="M18" t="n">
-        <v>0.639</v>
+        <v>-1.2497</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1857</v>
+        <v>-0.6354</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4533</v>
+        <v>-0.6143</v>
       </c>
       <c r="P18" t="n">
         <v>-0.1853</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.8529</v>
+        <v>-1.1117</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6676</v>
+        <v>0.9264</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4637</v>
+        <v>0.116</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4377</v>
+        <v>0.1595</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0259</v>
+        <v>-0.0435</v>
       </c>
       <c r="V18" t="n">
-        <v>1.2589</v>
+        <v>-0.63</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2589</v>
+        <v>-0.3155</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. RIBEIROS CARREIRAS</t>
+          <t>A. GALLEGO CONTRERAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.1896</v>
+        <v>-1.3381</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1471</v>
+        <v>-0.0047</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3367</v>
+        <v>-1.3335</v>
       </c>
       <c r="G19" t="n">
-        <v>2.7617</v>
+        <v>-1.3941</v>
       </c>
       <c r="H19" t="n">
-        <v>0.5026</v>
+        <v>-0.9088000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>2.2592</v>
+        <v>-0.4853</v>
       </c>
       <c r="J19" t="n">
-        <v>4.7765</v>
+        <v>0.1172</v>
       </c>
       <c r="K19" t="n">
-        <v>1.55</v>
+        <v>0.0342</v>
       </c>
       <c r="L19" t="n">
-        <v>3.2266</v>
+        <v>0.0829</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.0148</v>
+        <v>-1.5113</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.0474</v>
+        <v>-0.9429999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.9674</v>
+        <v>-0.5683</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.891</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.0382</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>-2.784</v>
+        <v>0.056</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.3679</v>
+        <v>-0.1219</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.4162</v>
+        <v>0.1778</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3144</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.9439</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.4873</v>
+        <v>-3.3402</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.1477</v>
+        <v>-2.0498</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3396</v>
+        <v>-1.2903</v>
       </c>
       <c r="G20" t="n">
         <v>-3.3013</v>
@@ -2014,13 +2014,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.186</v>
+        <v>-0.0389</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2736</v>
+        <v>-0.1756</v>
       </c>
       <c r="U20" t="n">
-        <v>0.08749999999999999</v>
+        <v>0.1368</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>F. GARRIDO SOTO</t>
+          <t>J. PINILLA NUNEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.6528</v>
+        <v>-3.4312</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6207</v>
+        <v>-1.3712</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.0321</v>
+        <v>-2.06</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.1493</v>
+        <v>-2.1312</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.8053</v>
+        <v>-1.2082</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3439</v>
+        <v>-0.923</v>
       </c>
       <c r="J21" t="n">
-        <v>0.0269</v>
+        <v>1.6969</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1805</v>
+        <v>0.1932</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2074</v>
+        <v>1.5036</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.1761</v>
+        <v>-3.8281</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.6248</v>
+        <v>-1.4014</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.5513</v>
+        <v>-2.4267</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9264</v>
+        <v>-2.7793</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9264</v>
+        <v>1.8529</v>
       </c>
       <c r="S21" t="n">
-        <v>0.7553</v>
+        <v>-0.3746</v>
       </c>
       <c r="T21" t="n">
-        <v>0.5944</v>
+        <v>-0.2888</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1609</v>
+        <v>-0.0858</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2589</v>
+        <v>0.0011</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.3155</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.9433</v>
+        <v>0.0011</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. PINILLA NUNEZ</t>
+          <t>J. MIAVIVULULU NZIKULU</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9454</v>
+        <v>-3.4877</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4691</v>
+        <v>-4.1388</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4763</v>
+        <v>0.6511</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.1312</v>
+        <v>-2.2257</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.2082</v>
+        <v>-0.9233</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.923</v>
+        <v>-1.3024</v>
       </c>
       <c r="J22" t="n">
-        <v>1.6969</v>
+        <v>-1.2003</v>
       </c>
       <c r="K22" t="n">
-        <v>0.1932</v>
+        <v>-0.7347</v>
       </c>
       <c r="L22" t="n">
-        <v>1.5036</v>
+        <v>-0.4656</v>
       </c>
       <c r="M22" t="n">
-        <v>-3.8281</v>
+        <v>-1.0254</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4014</v>
+        <v>-0.1885</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.4267</v>
+        <v>-0.8368</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.9264</v>
+        <v>-0.3706</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.7793</v>
+        <v>-2.9646</v>
       </c>
       <c r="R22" t="n">
-        <v>1.8529</v>
+        <v>2.594</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8889</v>
+        <v>-0.577</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.3867</v>
+        <v>0.0261</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5022</v>
+        <v>-0.6031</v>
       </c>
       <c r="V22" t="n">
-        <v>0.0011</v>
+        <v>-0.3144</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.0011</v>
+        <v>-0.3144</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. MIAVIVULULU NZIKULU</t>
+          <t>F. GARRIDO SOTO</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.2173</v>
+        <v>-4.2816</v>
       </c>
       <c r="E23" t="n">
-        <v>-5.3139</v>
+        <v>-1.3062</v>
       </c>
       <c r="F23" t="n">
-        <v>0.09669999999999999</v>
+        <v>-2.9754</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.2257</v>
+        <v>-3.1493</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.9233</v>
+        <v>-1.8053</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.3024</v>
+        <v>-1.3439</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.2003</v>
+        <v>0.0269</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7347</v>
+        <v>-0.1805</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.4656</v>
+        <v>0.2074</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.0254</v>
+        <v>-3.1761</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.1885</v>
+        <v>-1.6248</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.8368</v>
+        <v>-1.5513</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3706</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.9646</v>
+        <v>-0.9264</v>
       </c>
       <c r="R23" t="n">
-        <v>2.594</v>
+        <v>0.9264</v>
       </c>
       <c r="S23" t="n">
-        <v>-2.3065</v>
+        <v>0.1265</v>
       </c>
       <c r="T23" t="n">
-        <v>-1.149</v>
+        <v>-0.0911</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1575</v>
+        <v>0.2176</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3144</v>
+        <v>-1.2589</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.3144</v>
+        <v>-0.9433</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-17.6316</v>
+        <v>-13.7145</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.1152</v>
+        <v>-6.1153</v>
       </c>
       <c r="F24" t="n">
-        <v>-11.5163</v>
+        <v>-7.599000000000002</v>
       </c>
       <c r="G24" t="n">
         <v>-7.715</v>
@@ -2299,10 +2299,10 @@
         <v>-5.567600000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>6.809800000000001</v>
+        <v>6.8098</v>
       </c>
       <c r="K24" t="n">
-        <v>3.931299999999999</v>
+        <v>3.931300000000001</v>
       </c>
       <c r="L24" t="n">
         <v>2.8784</v>
@@ -2314,7 +2314,7 @@
         <v>-6.0783</v>
       </c>
       <c r="O24" t="n">
-        <v>-8.446300000000001</v>
+        <v>-8.446299999999999</v>
       </c>
       <c r="P24" t="n">
         <v>-4.632199999999999</v>
@@ -2326,16 +2326,16 @@
         <v>14.823</v>
       </c>
       <c r="S24" t="n">
-        <v>-5.2851</v>
+        <v>-1.3678</v>
       </c>
       <c r="T24" t="n">
-        <v>0.5534999999999999</v>
+        <v>0.5536000000000003</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.8386</v>
+        <v>-1.9213</v>
       </c>
       <c r="V24" t="n">
-        <v>0.0006000000000000449</v>
+        <v>0.000600000000000156</v>
       </c>
       <c r="W24" t="n">
         <v>5.9766</v>
